--- a/工作紀錄.xlsx
+++ b/工作紀錄.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ian32\Downloads\final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0999ADD8-7160-4388-8257-6FAFC7B36049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EF829F-7B7C-4E3D-9100-80DF354035A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="70">
-  <si>
-    <t>第一版</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="240">
   <si>
     <t>PS C:\Users\ian32\Downloads\final&gt; &amp; C:/Users/ian32/anaconda3/envs/dm/python.exe c:/Users/ian32/Downloads/final/run.py</t>
   </si>
@@ -58,9 +54,6 @@
     <t>準備訓練資料...</t>
   </si>
   <si>
-    <t>選定的特徵數量: 39</t>
-  </si>
-  <si>
     <t>訓練樣本數: 1760309</t>
   </si>
   <si>
@@ -112,57 +105,12 @@
     <t>Early stopping, best iteration is:</t>
   </si>
   <si>
-    <t>[1]     training's binary_logloss: 17.5232      training's auc: 0.766157  training's average_precision: 0.00343419 valid_1's binary_logloss: 17.5402 valid_1's auc: 0.710152  valid_1's average_precision: 0.00285361</t>
-  </si>
-  <si>
     <t>前10個最重要特徵:</t>
   </si>
   <si>
-    <t xml:space="preserve">           feature  importance</t>
-  </si>
-  <si>
-    <t>0           domain           6</t>
-  </si>
-  <si>
-    <t>16         weekday           3</t>
-  </si>
-  <si>
-    <t>8   ad_slot_height           2</t>
-  </si>
-  <si>
-    <t>15            hour           2</t>
-  </si>
-  <si>
-    <t>12      user_agent           2</t>
-  </si>
-  <si>
-    <t>9              url           2</t>
-  </si>
-  <si>
-    <t>19       tag_10006           2</t>
-  </si>
-  <si>
-    <t>17       ip_prefix           1</t>
-  </si>
-  <si>
-    <t>5      creative_id           1</t>
-  </si>
-  <si>
-    <t>11     ad_exchange           1</t>
-  </si>
-  <si>
-    <t>重要特徵 (重要性 &gt; 10) 數量: 0</t>
-  </si>
-  <si>
     <t>驗證集評估指標:</t>
   </si>
   <si>
-    <t>- AUC: 0.6994</t>
-  </si>
-  <si>
-    <t>- Average Precision: 0.0016</t>
-  </si>
-  <si>
     <t>CTR 模型訓練完成。</t>
   </si>
   <si>
@@ -193,49 +141,610 @@
     <t>測試集預處理完成。</t>
   </si>
   <si>
-    <t>已處理 50000/433409 筆競價請求. 剩餘總預算: 3336.00. 出價次數: 832. 假設花費: 1664.00</t>
-  </si>
-  <si>
-    <t>已處理 100000/433409 筆競價請求. 剩餘總預算: 2712.00. 出價次數: 1144. 假設花費: 2288.00</t>
-  </si>
-  <si>
-    <t>已處理 150000/433409 筆競價請求. 剩餘總預算: 2296.00. 出價次數: 1352. 假設花費: 2704.00</t>
-  </si>
-  <si>
-    <t>已處理 200000/433409 筆競價請求. 剩餘總預算: 1880.00. 出價次數: 1560. 假設花費: 3120.00</t>
-  </si>
-  <si>
-    <t>已處理 250000/433409 筆競價請求. 剩餘總預算: 1464.00. 出價次數: 1768. 假設花費: 3536.00</t>
-  </si>
-  <si>
-    <t>已處理 300000/433409 筆競價請求. 剩餘總預算: 1048.00. 出價次數: 1976. 假設花費: 3952.00</t>
-  </si>
-  <si>
-    <t>已處理 350000/433409 筆競價請求. 剩餘總預算: 632.00. 出價次數: 2184. 假設花費: 4368.00</t>
-  </si>
-  <si>
-    <t>已處理 400000/433409 筆競價請求. 剩餘總預算: 216.00. 出價次數: 2392. 假設花費: 4784.00</t>
-  </si>
-  <si>
-    <t>Day1 出價完成，結果已儲存至: M36134016_day1.csv</t>
-  </si>
-  <si>
-    <t>總出價次數 (paying_price &gt; 0): 2496</t>
-  </si>
-  <si>
-    <t>總出價金額 (假設都贏得且按此價格支付): 4992</t>
-  </si>
-  <si>
-    <t>剩餘總預算: 8.00</t>
-  </si>
-  <si>
-    <t>=== 執行完成 ===</t>
-  </si>
-  <si>
-    <t>結果已儲存至: M36134016_day1.csv</t>
-  </si>
-  <si>
-    <t>PS C:\Users\ian32\Downloads\final&gt;</t>
+    <t>第一次提交檔案內容預覽：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                             bid_id  paying_price</t>
+  </si>
+  <si>
+    <t>0  a21183e54eb7f97290ec6e549030bfb2            46</t>
+  </si>
+  <si>
+    <t>1  c91caab7cad159d5a8efbd475e2d794f            51</t>
+  </si>
+  <si>
+    <t>2  d4ef40f2d9d75f3bd56b53a2c6f7ec33             0</t>
+  </si>
+  <si>
+    <t>3  bedec93fafd04ad92b4685b0b8d4b697             0</t>
+  </si>
+  <si>
+    <t>4  8f264b322913f4263e92247253541501             0</t>
+  </si>
+  <si>
+    <t>5  a93d1ff92fc45849b193b6742aa3b4b3             0</t>
+  </si>
+  <si>
+    <t>6  b82a5d1d034bbe6fed40752e984aaa61             0</t>
+  </si>
+  <si>
+    <t>7  8fc398ee3b5719dfe948c9fc9351047d             0</t>
+  </si>
+  <si>
+    <t>8  49ac446c1f999d9527378763fc8f3e1e             0</t>
+  </si>
+  <si>
+    <t>9  cc9a83faf4d464da90597de71051a383             0</t>
+  </si>
+  <si>
+    <t>檔案形狀: (433409, 2)</t>
+  </si>
+  <si>
+    <t>欄位: ['bid_id', 'paying_price']</t>
+  </si>
+  <si>
+    <t>第一次提交反饋結果：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                             bid_id  paying_price  click</t>
+  </si>
+  <si>
+    <t>0  2763f53b74c8ea2ee0acab517fda85d7            20  False</t>
+  </si>
+  <si>
+    <t>1  af457e8682a17f1a23e07467031f717f            20  False</t>
+  </si>
+  <si>
+    <t>2  f58a13a1a61950312434fde73fd1f55d            50  False</t>
+  </si>
+  <si>
+    <t>3  9df40d390e7b5eae4b3c4e268d426875             1  False</t>
+  </si>
+  <si>
+    <t>4  6ea471b706f6e547206b2583d9d2fe41             1  False</t>
+  </si>
+  <si>
+    <t>5  a70a04f3616093515de4f2ae4bdf40c6             1  False</t>
+  </si>
+  <si>
+    <t>6  7287f2c806d2757c6ebe3d057f62b764             1  False</t>
+  </si>
+  <si>
+    <t>7  b37a5753f2737d13dc93549cce1fbffb             1  False</t>
+  </si>
+  <si>
+    <t>8   52db6af5f96f89e2cbfb9c8f93788fb             3  False</t>
+  </si>
+  <si>
+    <t>9  ba0b3727098b6a61fe09a9ef5d610d66             1  False</t>
+  </si>
+  <si>
+    <t>檔案形狀: (58, 3)</t>
+  </si>
+  <si>
+    <t>欄位: ['bid_id', 'paying_price', 'click']</t>
+  </si>
+  <si>
+    <t>第二天測試資料預覽：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                domain  ...                   ad_slot_id</t>
+  </si>
+  <si>
+    <t>0                  NaN  ...                   3663897446</t>
+  </si>
+  <si>
+    <t>1  trqRTuMvjTN7X9KbuKz  ...                   2536830969</t>
+  </si>
+  <si>
+    <t>2                  NaN  ...                   1758547350</t>
+  </si>
+  <si>
+    <t>3  trqRTuMvjTN7X9KbuKz  ...                   3195670606</t>
+  </si>
+  <si>
+    <t>4         eS9rt6k0MIdb  ...  mm_10748135_808827_11091222</t>
+  </si>
+  <si>
+    <t>[5 rows x 20 columns]</t>
+  </si>
+  <si>
+    <t>檔案形狀: (436648, 20)</t>
+  </si>
+  <si>
+    <t>欄位: ['domain', 'ad_slot_format', 'ip', 'anonymous_url_id', 'key_page_url', 'city', 'ad_slot_width', 'user_tags', 'creative_id', 'bidding_price', 'timestamp', 'bid_id', 'ad_slot_visibility', 'ad_slot_height', 'url', 'region', 'ad_exchange', 'user_agent', 'ad_slot_floor_price', 'ad_slot_id']</t>
+  </si>
+  <si>
+    <t>PS C:\Users\ian32\Downloads\final&gt; &amp; C:/Users/ian32/anaconda3/envs/dm/python.exe c:/Users/ian32/Downloads/final/show.py</t>
+  </si>
+  <si>
+    <t>=== 出價 vs 實際得標價分析 ===</t>
+  </si>
+  <si>
+    <t>📊 找到 58 筆可比較的記錄</t>
+  </si>
+  <si>
+    <t>1. 基本統計:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   我的出價 - 平均: 47.86, 中位數: 49.00, 範圍: 29-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   實際得標價 - 平均: 12.19, 中位數: 1.00, 範圍: 1-50</t>
+  </si>
+  <si>
+    <t>2. 出價差異分析:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   平均差異: 35.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   差異標準差: 18.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   出價/得標價比率 - 平均: 28.91</t>
+  </si>
+  <si>
+    <t>3. 出價策略分析:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   出價過高: 58 筆 (100.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   出價過低: 0 筆 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   出價剛好: 0 筆 (0.0%)</t>
+  </si>
+  <si>
+    <t>4. 詳細比較 (前20筆):</t>
+  </si>
+  <si>
+    <t>--------------------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                          bid_id  我的出價  實際得標價  差異  是否點擊</t>
+  </si>
+  <si>
+    <t>2763f53b74c8ea2ee0acab517fda85d7    39     20  19 False</t>
+  </si>
+  <si>
+    <t>af457e8682a17f1a23e07467031f717f    40     20  20 False</t>
+  </si>
+  <si>
+    <t>f58a13a1a61950312434fde73fd1f55d    55     50   5 False</t>
+  </si>
+  <si>
+    <t>9df40d390e7b5eae4b3c4e268d426875    47      1  46 False</t>
+  </si>
+  <si>
+    <t>6ea471b706f6e547206b2583d9d2fe41    50      1  49 False</t>
+  </si>
+  <si>
+    <t>a70a04f3616093515de4f2ae4bdf40c6    54      1  53 False</t>
+  </si>
+  <si>
+    <t>7287f2c806d2757c6ebe3d057f62b764    48      1  47 False</t>
+  </si>
+  <si>
+    <t>b37a5753f2737d13dc93549cce1fbffb    58      1  57 False</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 52db6af5f96f89e2cbfb9c8f93788fb    52      3  49 False</t>
+  </si>
+  <si>
+    <t>ba0b3727098b6a61fe09a9ef5d610d66    49      1  48 False</t>
+  </si>
+  <si>
+    <t>392f48ecc834ca6456e532df6dd4165f    49      1  48 False</t>
+  </si>
+  <si>
+    <t>582f4016ff4e3334ebb497027e965b1e    49      1  48 False</t>
+  </si>
+  <si>
+    <t>a318cc2548a6ab5747d586ac31d6ccf3    59      1  58 False</t>
+  </si>
+  <si>
+    <t>15d88c656298763c50fb843f15578983    52      1  51 False</t>
+  </si>
+  <si>
+    <t>302702a45c541ace96bb52876e97f70f    48      1  47 False</t>
+  </si>
+  <si>
+    <t>b33d08a73003b02986912113c56f54ad    52      1  51 False</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 34ab4546d8a00ddd7ae5994ed2da06e    50      1  49 False</t>
+  </si>
+  <si>
+    <t>b1e8b3446fd3683afedcf25d45821d32    50      1  49 False</t>
+  </si>
+  <si>
+    <t>3a5cf779298a27943c859d07e7a133de    48      1  47 False</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 86ffb3690a11a4d86da70293b00e4aa    45      1  44 False</t>
+  </si>
+  <si>
+    <t>5. 出價效率分析:</t>
+  </si>
+  <si>
+    <t>c:\Users\ian32\Downloads\final\show.py:75: FutureWarning: The default of observed=False is deprecated and will be changed to True in a future version of pandas. Pass observed=False to retain current behavior or observed=True to adopt the future default and silence this warning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  diff_analysis = merged.groupby('diff_category').agg({</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               出價次數  點擊次數  點擊率%</t>
+  </si>
+  <si>
+    <t>diff_category</t>
+  </si>
+  <si>
+    <t>低估&gt;10             0     0   NaN</t>
+  </si>
+  <si>
+    <t>低估5-10            0     0   NaN</t>
+  </si>
+  <si>
+    <t>低估&lt;5              0     0   NaN</t>
+  </si>
+  <si>
+    <t>高估&lt;5              9     0   0.0</t>
+  </si>
+  <si>
+    <t>高估5-10            0     0   NaN</t>
+  </si>
+  <si>
+    <t>高估&gt;10            49     0   0.0</t>
+  </si>
+  <si>
+    <t>6. 過度出價損失: 2069 元</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   可能因出價太低錯失的機會: 0 次</t>
+  </si>
+  <si>
+    <t>選定的特徵數量: 41</t>
+  </si>
+  <si>
+    <t>執行資料採樣，平衡正負樣本比例...</t>
+  </si>
+  <si>
+    <t>採樣後訓練集大小: 6330, 正樣本比例: 16.67%</t>
+  </si>
+  <si>
+    <t>[1]     training's binary_logloss: 0.450874     training's auc: 0.752386        training's average_precision: 0.350731 valid_1's binary_logloss: 0.21315       valid_1's auc: 0.716287        valid_1's average_precision: 0.00193799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        feature  importance</t>
+  </si>
+  <si>
+    <t>17    ip_prefix          13</t>
+  </si>
+  <si>
+    <t>40  domain_time           8</t>
+  </si>
+  <si>
+    <t>12   user_agent           6</t>
+  </si>
+  <si>
+    <t>15         hour           4</t>
+  </si>
+  <si>
+    <t>16      weekday           3</t>
+  </si>
+  <si>
+    <t>14   ad_slot_id           3</t>
+  </si>
+  <si>
+    <t>0        domain           3</t>
+  </si>
+  <si>
+    <t>20    tag_10110           3</t>
+  </si>
+  <si>
+    <t>5   creative_id           3</t>
+  </si>
+  <si>
+    <t>10       region           2</t>
+  </si>
+  <si>
+    <t>重要特徵 (重要性 &gt; 10) 數量: 1</t>
+  </si>
+  <si>
+    <t>- AUC: 0.7163</t>
+  </si>
+  <si>
+    <t>- Average Precision: 0.0019</t>
+  </si>
+  <si>
+    <t>CTR預測結果統計:</t>
+  </si>
+  <si>
+    <t>- 平均值: 0.19235369907472177</t>
+  </si>
+  <si>
+    <t>- 最小值: 0.1617264824934398</t>
+  </si>
+  <si>
+    <t>- 最大值: 0.19318627909457722</t>
+  </si>
+  <si>
+    <t>- 高於閾值(0.0001)的比例: 100.00%</t>
+  </si>
+  <si>
+    <t>Win-Price預測結果統計:</t>
+  </si>
+  <si>
+    <t>- 平均值: 54.765445492009</t>
+  </si>
+  <si>
+    <t>- 最小值: 28.609428763699526</t>
+  </si>
+  <si>
+    <t>- 最大值: 856.0929659028064</t>
+  </si>
+  <si>
+    <t>Win-Price 預測用特徵 NaN 檢查：</t>
+  </si>
+  <si>
+    <t>domain                 0</t>
+  </si>
+  <si>
+    <t>ad_slot_format         0</t>
+  </si>
+  <si>
+    <t>anonymous_url_id       0</t>
+  </si>
+  <si>
+    <t>city                   0</t>
+  </si>
+  <si>
+    <t>ad_slot_width          0</t>
+  </si>
+  <si>
+    <t>creative_id            0</t>
+  </si>
+  <si>
+    <t>ad_slot_visibility     0</t>
+  </si>
+  <si>
+    <t>ad_slot_height         0</t>
+  </si>
+  <si>
+    <t>url                    0</t>
+  </si>
+  <si>
+    <t>region                 0</t>
+  </si>
+  <si>
+    <t>ad_exchange            0</t>
+  </si>
+  <si>
+    <t>user_agent             0</t>
+  </si>
+  <si>
+    <t>ad_slot_floor_price    0</t>
+  </si>
+  <si>
+    <t>ad_slot_id             0</t>
+  </si>
+  <si>
+    <t>dtype: int64</t>
+  </si>
+  <si>
+    <t>Win-Price 預測用特徵型態：</t>
+  </si>
+  <si>
+    <t>domain                   int32</t>
+  </si>
+  <si>
+    <t>ad_slot_format           int64</t>
+  </si>
+  <si>
+    <t>anonymous_url_id       float64</t>
+  </si>
+  <si>
+    <t>city                     int32</t>
+  </si>
+  <si>
+    <t>ad_slot_width            int64</t>
+  </si>
+  <si>
+    <t>creative_id              int32</t>
+  </si>
+  <si>
+    <t>ad_slot_visibility       int64</t>
+  </si>
+  <si>
+    <t>ad_slot_height           int64</t>
+  </si>
+  <si>
+    <t>url                      int32</t>
+  </si>
+  <si>
+    <t>region                   int32</t>
+  </si>
+  <si>
+    <t>ad_exchange              int32</t>
+  </si>
+  <si>
+    <t>user_agent               int32</t>
+  </si>
+  <si>
+    <t>ad_slot_floor_price      int64</t>
+  </si>
+  <si>
+    <t>ad_slot_id               int32</t>
+  </si>
+  <si>
+    <t>dtype: object</t>
+  </si>
+  <si>
+    <t>已處理 50000/433409 筆競價請求. 剩餘總預算: 4208.00. 出價次數: 16. 假設花費: 792.00</t>
+  </si>
+  <si>
+    <t>已處理 100000/433409 筆競價請求. 剩餘總預算: 3319.00. 出價次數: 34. 假設花費: 1681.00</t>
+  </si>
+  <si>
+    <t>已處理 150000/433409 筆競價請求. 剩餘總預算: 2859.00. 出價次數: 44. 假設花費: 2141.00</t>
+  </si>
+  <si>
+    <t>已處理 200000/433409 筆競價請求. 剩餘總預算: 2336.00. 出價次數: 55. 假設花費: 2664.00</t>
+  </si>
+  <si>
+    <t>已處理 250000/433409 筆競價請求. 剩餘總預算: 1622.00. 出價次數: 70. 假設花費: 3378.00</t>
+  </si>
+  <si>
+    <t>已處理 300000/433409 筆競價請求. 剩餘總預算: 982.00. 出價次數: 84. 假設花費: 4018.00</t>
+  </si>
+  <si>
+    <t>已處理 350000/433409 筆競價請求. 剩餘總預算: 596.00. 出價次數: 92. 假設花費: 4404.00</t>
+  </si>
+  <si>
+    <t>已處理 400000/433409 筆競價請求. 剩餘總預算: 365.00. 出價次數: 97. 假設花費: 4635.00</t>
+  </si>
+  <si>
+    <t>Day1 出價完成，結果已儲存至: M36134016_day1_20250617_130314.csv</t>
+  </si>
+  <si>
+    <t>總出價次數 (paying_price &gt; 0): 99</t>
+  </si>
+  <si>
+    <t>總出價金額 (假設都贏得且按此價格支付): 4720</t>
+  </si>
+  <si>
+    <t>剩餘總預算: 280.00</t>
+  </si>
+  <si>
+    <t>=== RTB 競價系統執行開始 ===</t>
+  </si>
+  <si>
+    <t>--- 步驟 1: 初始化系統 ---</t>
+  </si>
+  <si>
+    <t>PS C:\Users\ian32\Downloads\final&gt; &amp; C:/Users/ian32/anaconda3/envs/dm/python.exe c:/Users/ian32/Downloads/final/main.py</t>
+  </si>
+  <si>
+    <t>--- 步驟 2: 載入資料 ---</t>
+  </si>
+  <si>
+    <t>測試集大小: (436648, 20)</t>
+  </si>
+  <si>
+    <t>--- 步驟 3: 特徵工程與訓練資料準備 ---</t>
+  </si>
+  <si>
+    <t>--- 步驟 4: 訓練 CTR 模型 ---</t>
+  </si>
+  <si>
+    <t>[1]     training's binary_logloss: 0.451516     training's auc: 0.748803        training's average_precision: 0.325623   valid_1's binary_logloss: 0.213931      valid_1's auc: 0.715552 valid_1's average_precision: 0.00172691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                feature  importance</t>
+  </si>
+  <si>
+    <t>17            ip_prefix          17</t>
+  </si>
+  <si>
+    <t>40          domain_time           8</t>
+  </si>
+  <si>
+    <t>14           ad_slot_id           5</t>
+  </si>
+  <si>
+    <t>10               region           4</t>
+  </si>
+  <si>
+    <t>3                  city           4</t>
+  </si>
+  <si>
+    <t>5           creative_id           4</t>
+  </si>
+  <si>
+    <t>15                 hour           4</t>
+  </si>
+  <si>
+    <t>16              weekday           3</t>
+  </si>
+  <si>
+    <t>13  ad_slot_floor_price           2</t>
+  </si>
+  <si>
+    <t>12           user_agent           2</t>
+  </si>
+  <si>
+    <t>- AUC: 0.7156</t>
+  </si>
+  <si>
+    <t>- Average Precision: 0.0017</t>
+  </si>
+  <si>
+    <t>--- 步驟 5: 訓練 Win-Price 模型 ---</t>
+  </si>
+  <si>
+    <t>--- 步驟 6: 執行 Day1 出價 ---</t>
+  </si>
+  <si>
+    <t>執行 Day2 出價...</t>
+  </si>
+  <si>
+    <t>- 平均值: 0.1926824442436051</t>
+  </si>
+  <si>
+    <t>- 平均值: 55.19947323298133</t>
+  </si>
+  <si>
+    <t>- 最小值: 28.68756720926584</t>
+  </si>
+  <si>
+    <t>- 最大值: 904.067883876348</t>
+  </si>
+  <si>
+    <t>已處理 50000/436648 筆競價請求. 剩餘總預算: 4356.00. 出價次數: 177. 假設花費: 644.00</t>
+  </si>
+  <si>
+    <t>已處理 100000/436648 筆競價請求. 剩餘總預算: 3183.00. 出價次數: 618. 假設花費: 1817.00</t>
+  </si>
+  <si>
+    <t>已處理 150000/436648 筆競價請求. 剩餘總預算: 2723.00. 出價次數: 718. 假設花費: 2277.00</t>
+  </si>
+  <si>
+    <t>費: 3588.00</t>
+  </si>
+  <si>
+    <t>已處理 300000/436648 筆競價請求. 剩餘總預算: 768.00. 出價次數: 1325. 假設花費: 4232.00</t>
+  </si>
+  <si>
+    <t>已處理 350000/436648 筆競價請求. 剩餘總預算: 354.00. 出價次數: 1571. 假設花費: 4646.00</t>
+  </si>
+  <si>
+    <t>已處理 400000/436648 筆競價請求. 剩餘總預算: 101.00. 出價次數: 1624. 假設花費: 4899.00</t>
+  </si>
+  <si>
+    <t>已處理 400000/436648 筆競價請求. 剩餘總預算: 101.00. 出價次數: 已處理 400000/436648 筆競價請求. 剩餘總預算: 101.00. 出價次數:  4899.00</t>
+  </si>
+  <si>
+    <t>Day1 出價完成，結果已儲存至: M36134016_day1_20250617_134406.csv</t>
+  </si>
+  <si>
+    <t>總出價次數: 1716</t>
+  </si>
+  <si>
+    <t>實際花費: 4991</t>
+  </si>
+  <si>
+    <t>預算利用率: 99.8%</t>
+  </si>
+  <si>
+    <t>平均出價: 2.91</t>
+  </si>
+  <si>
+    <t>出價範圍: 1 - 5</t>
+  </si>
+  <si>
+    <t>剩餘總預算: 9.00</t>
   </si>
 </sst>
 </file>
@@ -560,440 +1069,1457 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C182"/>
+  <sheetFormatPr defaultColWidth="154.75" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.625" customWidth="1"/>
+    <col min="2" max="2" width="5.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
+      <c r="B53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
+      <c r="B60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C61" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" t="s">
+        <v>94</v>
+      </c>
+      <c r="C66" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" t="s">
+        <v>95</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>98</v>
+      </c>
+      <c r="C70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" t="s">
+        <v>100</v>
+      </c>
+      <c r="C72" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" t="s">
+        <v>103</v>
+      </c>
+      <c r="C75" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" t="s">
+        <v>105</v>
+      </c>
+      <c r="C77" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" t="s">
+        <v>111</v>
+      </c>
+      <c r="C83" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>112</v>
+      </c>
+      <c r="C84" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>136</v>
+      </c>
+      <c r="C85" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>137</v>
+      </c>
+      <c r="B86" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>139</v>
+      </c>
+      <c r="B88" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>141</v>
+      </c>
+      <c r="B91" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" t="s">
+        <v>120</v>
+      </c>
+      <c r="C93" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>142</v>
+      </c>
+      <c r="B94" t="s">
+        <v>121</v>
+      </c>
+      <c r="C94" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" t="s">
+        <v>122</v>
+      </c>
+      <c r="C95" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>123</v>
+      </c>
+      <c r="C96" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>30</v>
+      </c>
+      <c r="C100" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>142</v>
+      </c>
+      <c r="C105" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>143</v>
+      </c>
+      <c r="C106" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C107" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C109" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>143</v>
+      </c>
+      <c r="C112" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C113" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C115" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C118" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>32</v>
+      </c>
+      <c r="C122">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C124">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
+      <c r="C126" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
+      <c r="C127" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B52" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B58" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B59" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B60" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B61" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B63" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B68" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B81" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B87" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B88" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B89" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B90" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B92" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B94" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B99" t="s">
-        <v>69</v>
+      <c r="C128" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>146</v>
+      </c>
+      <c r="C131" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
